--- a/extenbooks/S604.xlsx
+++ b/extenbooks/S604.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S604.xlsx
+++ b/extenbooks/S604.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,54 +954,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S604-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S604 — Total Tax Workers (T_w)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `total_tax_workers`</t>
+          <t># S604 — Total Tax Workers (T_w)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `total_tax_workers`</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1018,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sum of personal + social insurance + sales/excise + property tax paid by workers. T_w is the negative term in the NSW identity.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1062,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Sum of personal + social insurance + sales/excise + property tax paid by workers. T_w is the negative term in the NSW identity.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1098,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=53.21B; 1989=1116.89B</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S604_total_tax_workers.py`. Both endpoints PASS.</t>
+          <t>1952=53.21B; 1989=1116.89B</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1146,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S604_total_tax_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1158,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S604_total_tax_workers.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1178,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S604.csv</t>
+          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1186,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S604_total_tax_workers.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S604_total_tax_workers.py</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1194,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S604.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S604.csv</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S604_total_tax_workers.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S604_total_tax_workers.py</t>
         </is>
       </c>
     </row>
@@ -1205,19 +1210,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S604.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S604_total_tax_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1250,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1261,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1289,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,196 +1317,295 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T_w = S601 (personal income tax workers) + S602 (social insurance tax workers) + S603 (property tax workers) + indirect taxes (sales/excise taxes allocated to workers). The indirect tax component is allocated proportional to worker consumption share, estimated from worker income relative to total consumption expenditure.</t>
+          <t>Our adjustment procedure involves two steps. First, we estimate the social benefit expenditures directed toward wage and salary earners by the state, the taxes paid by them, and the difference between the two, which is the net transfer (a positive number when benefits exceed taxes and negative in the opposite case). The true compensation of wage and salary earners is their apparent compensation plus the net transfer.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Section 5.9, page 137; HDARP chunk_16 lines 79-83</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Component series S601, S602, S603 provide three direct tax components. Sales and excise taxes from NIPA Table 3.1 (indirect business tax and nontax accruals) and Table 3.3. Worker consumption share derived from compensation data and personal consumption expenditure (NIPA Table 2.1).</t>
+          <t>Appendix N lists the detailed calculations of our social accounting of taxes and benefits. Figure 5.22 shows the resulting tax and benefit rates (relative to total employee compensation), and Figure 5.23 shows the corresponding net transfer rate for the United States from 1952 to 1985.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Tables 2.1, 3.1, 3.3</t>
+          <t>ST_1994, Section 5.9 (Empirical Results), page 141; HDARP chunk_16 line 117</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Total worker tax burden as a ratio to employee compensation (T/EC) rose from approximately 0.18 in 1952 to 0.32 by 1989, a 78% increase. The growth was driven primarily by rising social insurance contributions and bracket creep in personal income taxes before indexation.</t>
+          <t>It is immediately evident that, for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures. As a result, the true rate of surplus value is generally higher than the apparent one (see Figure 5.24).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Section 5.9 key finding, page 141; HDARP chunk_16 lines 123-125</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The key methodological divergence across studies is sales/excise tax treatment. AS2 includes sales and excise taxes in the worker tax burden; Tonak's original framework excludes them. This is the primary source of the AS2-Tonak correlation drop (r=0.611 vs Moos-Tonak r=0.876). Moos includes indirect taxes similarly to AS2.</t>
+          <t>T1 = Total taxes from labor 1964 = 76.2 billion dollars (Social insurance 30.1 + Personal income 36.4 + Other 2.8 + Motor vehicle 0.8 + Personal property 6.1).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Table N.1 Taxes total, 1964 benchmark; HDARP chunk_38 lines 296-306</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The sales/excise tax inclusion is theoretically justified because workers bear these taxes through consumption. However, the allocation ratio (worker consumption / total consumption) is an approximation. Sensitivity analysis shows that excluding indirect taxes shifts NSW toward less negative values but does not change the qualitative finding of predominantly negative NSW.</t>
+          <t>T1 = Total taxes from labor 1964 = 76.2 billion dollars (Social insurance 30.1 + Personal income 36.4 + Other 2.8 + Motor vehicle 0.8 + Personal property 6.1).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Table N.1 Taxes total; KB chunk_38 lines 296-306</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T_w = S601 + S602 + S603 + (sales_excise_taxes × worker_consumption_share). Worker consumption share ≈ W / personal_consumption_expenditure, bounded [0,1].</t>
+          <t>Tax rate (T1/EC): 1952: 0.18 (18%) -&gt; 1989: 0.32 (32%); Increased 1.8x (workers paid more taxes).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6</t>
+          <t>ST_1994, Table N.2 (Tax rate trend 1952-89); KB chunk_38 lines 363-365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-008 (2026-04-09): The income-proportional tax allocation (T_w = taxes × W_p/PI) is the formula that applies to all T60x components summed in S604. HDARP extraction of Section 3.3 (pages 63-65) documents the NRYwp net royalty framework: the total tax allocation to workers in S604 is the empirical implementation of that framework at the aggregate level. P09 methodology verified correct.</t>
+          <t>Excluded taxes (not levied on workers - footnote 2): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Group I - Social security taxes (100% from workers): Employee contributions; Employer contributions (deducted before workers receive income); Net government receipts from lotteries (treated as direct tax - footnote 1).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group I); KB chunk_38 lines 257-260</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Total worker taxes sum personal income tax (S601), social insurance (S602), property tax (S603), and indirect sales/excise taxes allocated by worker consumption share. Tax/EC ratio rose 78% from 0.18 to 0.32 over 1952-1989. DEC-008 confirms T_w = taxes × W_p/PI income-proportional allocation is the correct methodology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T_w = S601 (personal income tax workers) + S602 (social insurance tax workers) + S603 (property tax workers) + indirect taxes (sales/excise taxes allocated to workers). The indirect tax component is allocated proportional to worker consumption share, estimated from worker income relative to total consumption expenditure.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Component series S601, S602, S603 provide three direct tax components. Sales and excise taxes from NIPA Table 3.1 (indirect business tax and nontax accruals) and Table 3.3. Worker consumption share derived from compensation data and personal consumption expenditure (NIPA Table 2.1).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Tables 2.1, 3.1, 3.3</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sales/excise tax inclusion is the main methodological divergence from Tonak benchmark</t>
+          <t>Total worker tax burden as a ratio to employee compensation (T/EC) rose from approximately 0.18 in 1952 to 0.32 by 1989, a 78% increase. The growth was driven primarily by rising social insurance contributions and bracket creep in personal income taxes before indexation.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Worker consumption share proxy is approximate</t>
+          <t>The key methodological divergence across studies is sales/excise tax treatment. AS2 includes sales and excise taxes in the worker tax burden; Tonak's original framework excludes them. This is the primary source of the AS2-Tonak correlation drop (r=0.611 vs Moos-Tonak r=0.876). Moos includes indirect taxes similarly to AS2.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tax bracket indexation (post-1985) changes the income tax growth dynamic</t>
+          <t>The sales/excise tax inclusion is theoretically justified because workers bear these taxes through consumption. However, the allocation ratio (worker consumption / total consumption) is an approximation. Sensitivity analysis shows that excluding indirect taxes shifts NSW toward less negative values but does not change the qualitative finding of predominantly negative NSW.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State-level tax variation not captured in national aggregates</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+          <t>T_w = S601 + S602 + S603 + (sales_excise_taxes × worker_consumption_share). Worker consumption share ≈ W / personal_consumption_expenditure, bounded [0,1].</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>decision_log_note</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09): The income-proportional tax allocation (T_w = taxes × W_p/PI) is the formula that applies to all T60x components summed in S604. HDARP extraction of Section 3.3 (pages 63-65) documents the NRYwp net royalty framework: the total tax allocation to workers in S604 is the empirical implementation of that framework at the aggregate level. P09 methodology verified correct.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S601</t>
-        </is>
-      </c>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S602</t>
+          <t>T1 = Total taxes from labor 1964 = 76.2 billion dollars (Social insurance 30.1 + Personal income 36.4 + Other 2.8 + Motor vehicle 0.8 + Personal property 6.1).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 Taxes total; KB chunk_38 lines 296-306</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1613,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S603</t>
+          <t>Tax rate (T1/EC): 1952: 0.18 (18%) -&gt; 1989: 0.32 (32%); Increased 1.8x (workers paid more taxes).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 (Tax rate trend 1952-89); KB chunk_38 lines 363-365</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1626,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S605</t>
+          <t>Excluded taxes (not levied on workers - footnote 2): Corporate profit taxes; Indirect business taxes; Estate and gift taxes (only apply to highest income levels).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N footnote 2; KB chunk_38 lines 268-271</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1639,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S606</t>
+          <t>Group I - Social security taxes (100% from workers): Employee contributions; Employer contributions (deducted before workers receive income); Net government receipts from lotteries (treated as direct tax - footnote 1).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group I); KB chunk_38 lines 257-260</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1652,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S607</t>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
         </is>
       </c>
     </row>
@@ -1525,41 +1665,150 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Total worker taxes sum personal income tax (S601), social insurance (S602), property tax (S603), and indirect sales/excise taxes allocated by worker consumption share. Tax/EC ratio rose 78% from 0.18 to 0.32 over 1952-1989. [internal-decision-record] confirms T_w = taxes × W_p/PI income-proportional allocation is the correct methodology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sales/excise tax inclusion is the main methodological divergence from Tonak benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Worker consumption share proxy is approximate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tax bracket indexation (post-1985) changes the income tax growth dynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>State-level tax variation not captured in national aggregates</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S601</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S602</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S603</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S605</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S606</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
@@ -1576,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1660,7 +1909,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1930,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 53.2083, "1989": 1116.8898}</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1954,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S604.xlsx
+++ b/extenbooks/S604.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
+          <t>**Book location**: Chapter 5 §5.9 ("The net transfer between workers and the state") + **Appendix N** (Tables N.1, N.2). *(There is NO "Chapter 6 — The Net Social Wage"; the earlier such citation and "Table 6.1 / Table6_1_TaxAccounts.csv" as a BOOK table were fabricated and are removed — see registry `fabricated_refs_removed`.)*</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `total_tax_workers`</t>
+          <t>**Source data**: `data/source/book_tables/Table6_1_TaxAccounts.csv` — a **BEA-API reconstruction** (file header: "Source: NIPA Tables 3.1, 3.2, 3.3, 2.1 via BEA API"), NOT a transcription of Appendix N.</t>
         </is>
       </c>
     </row>
@@ -1018,23 +1018,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Units**: billions_usd</t>
+          <t>**Units**: billions_usd · **Period**: 1952–1989 · **Content Type**: time_series · **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1042,27 +1038,27 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>T_w = total taxes borne by workers = personal income tax + social insurance + property + **sales/excise** (as reconstructed). It is the T1 term of the book's net-transfer identity NSW = B_w + G_w − T_w.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sum of personal + social insurance + sales/excise + property tax paid by workers. T_w is the negative term in the NSW identity.</t>
+          <t>Pass-through: `L01_S604` reads `Table6_1_TaxAccounts.csv:total_tax_workers`, divides by 1000 (millions→billions); `P02_S604` adds stage/provenance. The `total_tax_workers` column already sums the components — no arithmetic in code.</t>
         </is>
       </c>
     </row>
@@ -1074,31 +1070,35 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>## Book anchor + DIVERGENCE (WP-B review 2026-07-01)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Book Appendix N **Table N.1 (1964)**: T1 = **76.2** (labor column = 30.1 soc.ins + 36.4 personal + 2.8 other + 0.8 motor vehicle + 6.1 property). Our S604(1964) = **111.06** = 37.06 + 22.39 + **40.76 (sales/excise)** + 10.84. **Excess +34.86, dominated by the +40.76 sales/excise term — indirect business taxes that Appendix N EXPLICITLY EXCLUDES** ("corporate profit taxes, indirect business taxes, and estate/gift taxes are excluded"). This is a **method divergence**, registered as **WP-B-DIV-S604-INDIRECT** + **WP-B-DIV-NSW-BASKET**. Removing the indirect term alone does not reproduce the book (it flips NSW positive; the benefit side also over-counts). A book-faithful S604 requires the Appendix-N Group I/II/III classification + annual labor shares (BEA SED data, not in the source tree) → G2-gated.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>Registry `reference_values` {1952: 53.21, 1989: 1116.89} are the construction's OWN endpoints (tautological self-check; 1964 not checked — this is why the +46% divergence was masked). Book anchor added: **1964 = 76.2** (documented divergence, not a passing gate). Tolerance class: `dollar_series`.</t>
         </is>
       </c>
     </row>
@@ -1110,55 +1110,71 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>data/source/book_tables/Table6_1_TaxAccounts.csv (:total_tax_workers)   [BEA-API reconstruction]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S604_total_tax_workers.py  (÷1000)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1952=53.21B; 1989=1116.89B</t>
+          <t xml:space="preserve">       └── data/intermediate/S604.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S604_total_tax_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S604_total_tax_workers.py`. Both endpoints PASS.</t>
+          <t xml:space="preserve">                 └── data/final/S604.csv → chopped/S604.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S604_total_tax_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1186,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1178,23 +1194,19 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 5 §5.9 + Appendix N (Tables N.1, N.2, pp.356–359). Methodology summarized from Shaikh &amp; Tonak (1987); labor shares from Tonak (1984).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S604_total_tax_workers.py</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S604.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1202,79 +1214,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S604_total_tax_workers.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 └── data/final/S604.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S604_total_tax_workers.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>## Citation</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+          <t>*Regenerated by WP-B comprehensive review 2026-07-01 (stale fabricated refs removed; +46% divergence adjudicated).*</t>
         </is>
       </c>
     </row>
